--- a/testdata/Robinhood test 2024.xlsx
+++ b/testdata/Robinhood test 2024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UN\fractals\VibeCoding\ClaudeCode\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26647D9B-6066-4EE3-96F8-CDB9DD30F42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6333B12-C26F-481B-B57E-C006B6BD6ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="5" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="692">
   <si>
     <t/>
   </si>
@@ -68,270 +68,16 @@
     <t>Proceeds from Broker and Barter Exchange Transactions</t>
   </si>
   <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">1099-B* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>OMB No. 1545-0715</t>
-    </r>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>02/11/2025</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Sales transactions are organized into sections according to term (long, short or undetermined) and covered status (covered or noncovered). For tax lots whose term is undetermined, use your historical</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-documents to establish the cost basis and date of purchase. The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Box 12, Check if basis reported to IRS</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> checkmark, is reflected as being checked in the title of the covered securities pages of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Forms</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-1099-B, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">short-term and long-term. The title pages of the noncovered securities pages for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Forms 1099-B</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> reflect that </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Box 12</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> is not being checked, as these securities are not being reported to the IRS.</t>
-    </r>
-  </si>
-  <si>
-    <t>Several columns include both an amount and a qualifying notation to its right. Where proceeds are the result of an option exercise or assignment, there is indication of whether the amount is N (net of
-option premium) or G (Gross). Accrued market discount and wash sale loss disallowed appear in the same column, identified by the letters D or W, respectively. Where you are not permitted to
-recognize a loss, an indication of X (change in control or capital structure) or Z (other corporate action) is used. The change in control condition is reported to the IRS for covered lots. Neither the
-disallowance of loss due to a corporate action nor the amount of gain or loss is reported to the IRS in any instance.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Some tax lots may have notations in the column of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Additional Information </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>because they require special treatment on your tax returns. Sales of securities such as Contingent Payment Debt Instruments</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-(CPDI) are marked as “Ordinary” because gains and losses on these instruments generally do not qualify as short- or long-term capital transactions. Similarly, lots noted as “3 - [X] Collectible” are</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-handled distinctly under the tax code. These conditions are reported to the IRS. You may wish to consult with your tax advisor, the IRS or your state tax authority regarding the proper treatment for</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-these scenarios. With further regard to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Box 3</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>, there is also a checkmark to indicate the proceeds of sale are from a Qualified Opportunity Zone Fund investment - a QOF. If the proceeds are from a QOF</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-the Additional Information column will reflect the following - “3 - [X] Proceeds from QOF.” The tax treatment for QOF investments can be complex and you may wish to consult your tax advisor about</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-such sales.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Closing of written options is presented in a distinct manner in accordance with IRS regulations. For these transactions the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Cost or other basis </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">(column 1e) is always presented as $0.00 and the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-Proceeds</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> (column 1d) is the net of the amount received when the option was written and the cost to close the position.</t>
-    </r>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>FATCA filing requirement [ ]</t>
@@ -839,51 +585,7 @@
     <t>Proceeds from Broker and Barter Exchange Transactions</t>
   </si>
   <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">1099-B* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>OMB No. 1545-0715</t>
-    </r>
-  </si>
-  <si>
     <t>(continued)</t>
-  </si>
-  <si>
-    <t>02/11/2025</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <r>
@@ -1307,38 +1009,6 @@
     <t>Proceeds from Broker and Barter Exchange Transactions</t>
   </si>
   <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t>107623092C</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">1099-B* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>OMB No. 1545-0715</t>
-    </r>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -1355,225 +1025,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Sales transactions are organized into sections according to term (long, short or undetermined) and covered status (covered or noncovered). For tax lots whose term is undetermined, use your historical</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-documents to establish the cost basis and date of purchase. The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Box 12, Check if basis reported to IRS</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> checkmark, is reflected as being checked in the title of the covered securities pages of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Forms</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-1099-B, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">short-term and long-term. The title pages of the noncovered securities pages for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Forms 1099-B</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> reflect that </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Box 12</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> is not being checked, as these securities are not being reported to the IRS.</t>
-    </r>
-  </si>
-  <si>
-    <t>Several columns include both an amount and a qualifying notation to its right. Where proceeds are the result of an option exercise or assignment, there is indication of whether the amount is N (net of
-option premium) or G (Gross). Accrued market discount and wash sale loss disallowed appear in the same column, identified by the letters D or W, respectively. Where you are not permitted to
-recognize a loss, an indication of X (change in control or capital structure) or Z (other corporate action) is used. The change in control condition is reported to the IRS for covered lots. Neither the
-disallowance of loss due to a corporate action nor the amount of gain or loss is reported to the IRS in any instance.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Some tax lots may have notations in the column of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Additional Information </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>because they require special treatment on your tax returns. Sales of securities such as Contingent Payment Debt Instruments</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-(CPDI) are marked as “Ordinary” because gains and losses on these instruments generally do not qualify as short- or long-term capital transactions. Similarly, lots noted as “3 - [X] Collectible” are</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-handled distinctly under the tax code. These conditions are reported to the IRS. You may wish to consult with your tax advisor, the IRS or your state tax authority regarding the proper treatment for</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-these scenarios. With further regard to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Box 3</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>, there is also a checkmark to indicate the proceeds of sale are from a Qualified Opportunity Zone Fund investment - a QOF. If the proceeds are from a QOF</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-the Additional Information column will reflect the following - “3 - [X] Proceeds from QOF.” The tax treatment for QOF investments can be complex and you may wish to consult your tax advisor about</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-such sales.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Closing of written options is presented in a distinct manner in accordance with IRS regulations. For these transactions the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Cost or other basis </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">(column 1e) is always presented as $0.00 and the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-Proceeds</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> (column 1d) is the net of the amount received when the option was written and the cost to close the position.</t>
-    </r>
   </si>
   <si>
     <t>FATCA filing requirement [ ]</t>
@@ -2084,38 +1535,6 @@
     <t>Proceeds from Broker and Barter Exchange Transactions</t>
   </si>
   <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t>107623092C</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">1099-B* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>OMB No. 1545-0715</t>
-    </r>
-  </si>
-  <si>
     <t>(continued)</t>
   </si>
   <si>
@@ -2945,38 +2364,6 @@
   </si>
   <si>
     <t>Proceeds from Broker and Barter Exchange Transactions</t>
-  </si>
-  <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t>107623092C</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">1099-B* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>OMB No. 1545-0715</t>
-    </r>
   </si>
   <si>
     <t>(continued)</t>
@@ -3559,7 +2946,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3610,12 +2997,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
@@ -3632,20 +3013,6 @@
     <font>
       <i/>
       <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="7"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -3742,7 +3109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3919,32 +3286,56 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3952,41 +3343,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4268,7 +3629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15"/>
@@ -4315,619 +3676,543 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="69" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="81">
-        <v>107623092</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="68" t="s">
-        <v>15</v>
-      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>2024</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="24"/>
+      <c r="C3" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="73"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+    </row>
+    <row r="5" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+    </row>
+    <row r="6" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="B6" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="C6" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="D6" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="E6" s="63" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="F6" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-    </row>
-    <row r="5" spans="1:10" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
+      <c r="G6" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-    </row>
-    <row r="6" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="75" t="s">
+      <c r="H6" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-    </row>
-    <row r="7" spans="1:10" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="76" t="s">
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-    </row>
-    <row r="8" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="77" t="s">
+      <c r="B7" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-    </row>
-    <row r="9" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="C7" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-    </row>
-    <row r="10" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="64" t="s">
+      <c r="D7" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="E7" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="F7" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="G7" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="69" t="s">
+      <c r="H7" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="69" t="s">
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+    </row>
+    <row r="8" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="69" t="s">
+      <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="69" t="s">
+      <c r="C8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
+      <c r="D8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="E8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="F8" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="G8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="H8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="69" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="B9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="69" t="s">
+      <c r="C9" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
+      <c r="D9" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="80" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="31">
+        <v>175</v>
+      </c>
+      <c r="C11" s="12">
+        <v>575.07000000000005</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="12">
+        <v>531.75</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="12">
+        <v>43.32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="73" t="s">
+      <c r="A12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="B12" s="31">
+        <v>790</v>
+      </c>
+      <c r="C12" s="12">
+        <v>2292.46</v>
+      </c>
+      <c r="D12" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E12" s="12">
+        <v>1807.12</v>
+      </c>
+      <c r="F12" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G12" s="12">
+        <v>485.34</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="4" t="s">
+    </row>
+    <row r="13" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="B13" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="C13" s="11">
+        <v>2867.53</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="E13" s="11">
+        <v>2338.87</v>
+      </c>
+      <c r="F13" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="31">
-        <v>175</v>
-      </c>
-      <c r="C15" s="12">
-        <v>575.07000000000005</v>
-      </c>
-      <c r="D15" s="32" t="s">
+      <c r="G13" s="11">
+        <v>528.66</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="12">
-        <v>531.75</v>
-      </c>
-      <c r="F15" s="32" t="s">
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="12">
-        <v>43.32</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="B14" s="63" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="C14" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="31">
-        <v>790</v>
-      </c>
-      <c r="C16" s="12">
-        <v>2292.46</v>
-      </c>
-      <c r="D16" s="32" t="s">
+      <c r="D14" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="12">
-        <v>1807.12</v>
-      </c>
-      <c r="F16" s="32" t="s">
+      <c r="E14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="12">
-        <v>485.34</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="H14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="11">
-        <v>2867.53</v>
-      </c>
-      <c r="D17" s="1" t="s">
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="11">
-        <v>2338.87</v>
-      </c>
-      <c r="F17" s="33" t="s">
+      <c r="B15" s="35">
+        <v>1</v>
+      </c>
+      <c r="C15" s="36">
+        <v>9.44</v>
+      </c>
+      <c r="D15" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="11">
-        <v>528.66</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="E15" s="36">
+        <v>9.77</v>
+      </c>
+      <c r="F15" s="37" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="74" t="s">
+      <c r="G15" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="H15" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="69" t="s">
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="69" t="s">
+      <c r="B16" s="63" t="s">
         <v>85</v>
       </c>
+      <c r="C16" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="35">
+        <v>1500</v>
+      </c>
+      <c r="C17" s="36">
+        <v>431.75</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="36">
+        <v>2340.96</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="39">
         <v>1</v>
       </c>
-      <c r="C19" s="36">
-        <v>9.44</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="36">
-        <v>9.77</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="69" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="35">
-        <v>1500</v>
-      </c>
-      <c r="C21" s="36">
-        <v>431.75</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="36">
-        <v>2340.96</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" s="38" t="s">
+      <c r="C19" s="5">
+        <v>1.26</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H21" s="34" t="s">
+      <c r="E19" s="12">
+        <v>1.59</v>
+      </c>
+      <c r="F19" s="32" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="74" t="s">
+      <c r="G19" s="12">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B22" s="69" t="s">
+    </row>
+    <row r="20" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="B20" s="39">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E20" s="12">
+        <v>1.59</v>
+      </c>
+      <c r="F20" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="G20" s="12">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F22" s="1" t="s">
+    </row>
+    <row r="21" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="B21" s="39">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="E21" s="12">
+        <v>1.59</v>
+      </c>
+      <c r="F21" s="32" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="G21" s="12">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="39">
+    </row>
+    <row r="22" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="40">
         <v>1</v>
       </c>
-      <c r="C23" s="5">
-        <v>1.26</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E23" s="12">
+      <c r="C22" s="22">
+        <v>0.99</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="41">
         <v>1.59</v>
       </c>
-      <c r="F23" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="12">
+      <c r="F22" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="41">
         <v>0</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="H22" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="39">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5">
-        <v>1.22</v>
-      </c>
-      <c r="D24" s="2" t="s">
+    </row>
+    <row r="23" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="12">
-        <v>1.59</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" s="12">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="39">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5">
-        <v>0.98</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E25" s="12">
-        <v>1.59</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" s="12">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="40">
-        <v>1</v>
-      </c>
-      <c r="C26" s="22">
-        <v>0.99</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" s="41">
-        <v>1.59</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="G26" s="41">
-        <v>0</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="63" t="s">
-        <v>132</v>
-      </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="12">
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4951,225 +4236,203 @@
   <sheetData>
     <row r="1" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="J1" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="80" t="s">
-        <v>143</v>
+      <c r="A2" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>132</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E2" s="81">
-        <v>107623092</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="H2" s="68" t="s">
-        <v>148</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>2024</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>149</v>
-      </c>
+      <c r="B3" s="24"/>
       <c r="C3" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="70" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" s="84" t="s">
-        <v>152</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>155</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="D3" s="73"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="43"/>
     </row>
     <row r="4" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
     </row>
     <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
+      <c r="A5" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="69" t="s">
-        <v>161</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>163</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>165</v>
-      </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
+      <c r="A6" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="72" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>185</v>
+      <c r="A9" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="66" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="66" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>164</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B10" s="31">
         <v>284</v>
@@ -5178,24 +4441,24 @@
         <v>304.18</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="E10" s="12">
         <v>449.67</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="B11" s="31">
         <v>1800</v>
@@ -5204,76 +4467,76 @@
         <v>1929.91</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="E11" s="12">
         <v>2642.04</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C12" s="11">
         <v>2238.54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="E12" s="11">
         <v>3098.07</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="83" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="69" t="s">
-        <v>207</v>
+      <c r="A13" s="82" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>186</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="B14" s="31">
         <v>15000</v>
@@ -5282,24 +4545,24 @@
         <v>1967.45</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="E14" s="12">
         <v>1853.7</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="G14" s="12">
         <v>113.75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="B15" s="31">
         <v>13100</v>
@@ -5308,86 +4571,86 @@
         <v>1556.68</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E15" s="12">
         <v>1612.12</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="C16" s="13">
         <v>3524.13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="E16" s="13">
         <v>3465.82</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="G16" s="13">
         <v>58.31</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="C17" s="46">
         <v>9071.39</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="E17" s="46">
         <v>11253.49</v>
       </c>
       <c r="F17" s="45" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="G17" s="47" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="63" t="s">
-        <v>233</v>
-      </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
+      <c r="A18" s="67" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5407,7 +4670,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29"/>
@@ -5422,675 +4685,603 @@
   <sheetData>
     <row r="1" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="J1" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
-        <v>243</v>
-      </c>
-      <c r="B2" s="80" t="s">
-        <v>244</v>
+      <c r="A2" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>223</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="E2" s="81" t="s">
-        <v>247</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>248</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="H2" s="68" t="s">
-        <v>250</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>2024</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="24"/>
+      <c r="C3" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" s="77" t="s">
+        <v>227</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+    </row>
+    <row r="5" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="75" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+    </row>
+    <row r="6" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="H7" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+    </row>
+    <row r="8" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="D8" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="E8" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="F8" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G8" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H8" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="H3" s="3" t="s">
+    </row>
+    <row r="9" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
+      <c r="B9" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-    </row>
-    <row r="5" spans="1:10" ht="52.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75" t="s">
+      <c r="C9" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-    </row>
-    <row r="6" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="75" t="s">
+      <c r="D9" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-    </row>
-    <row r="7" spans="1:10" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="76" t="s">
+      <c r="E9" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-    </row>
-    <row r="8" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="77" t="s">
+      <c r="F9" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-    </row>
-    <row r="9" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="G9" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-    </row>
-    <row r="10" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="64" t="s">
+      <c r="H9" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B10" s="69" t="s">
+    </row>
+    <row r="10" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="B10" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="C10" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E10" s="69" t="s">
+      <c r="D10" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F10" s="69" t="s">
+      <c r="E10" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="G10" s="69" t="s">
+      <c r="F10" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="H10" s="69" t="s">
+      <c r="G10" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-    </row>
-    <row r="11" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="65" t="s">
+      <c r="H10" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B11" s="69" t="s">
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="C11" s="69" t="s">
+      <c r="B11" s="49">
+        <v>2.4329999999999999E-5</v>
+      </c>
+      <c r="C11" s="36">
+        <v>1.26</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="E11" s="36">
+        <v>1.01</v>
+      </c>
+      <c r="F11" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="G11" s="36">
+        <v>0.25</v>
+      </c>
+      <c r="H11" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="F11" s="69" t="s">
+    </row>
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="81" t="s">
         <v>277</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="B12" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="H11" s="69" t="s">
+      <c r="C12" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-    </row>
-    <row r="12" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="D12" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="E12" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="F12" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="H12" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="F12" s="14" t="s">
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="B13" s="50">
+        <v>0.16664499999999999</v>
+      </c>
+      <c r="C13" s="36">
+        <v>420.12</v>
+      </c>
+      <c r="D13" s="37" t="s">
         <v>286</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="E13" s="36">
+        <v>400.19</v>
+      </c>
+      <c r="F13" s="34" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="G13" s="36">
+        <v>19.93</v>
+      </c>
+      <c r="H13" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="B13" s="9" t="s">
+    </row>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="81" t="s">
         <v>289</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="B14" s="63" t="s">
         <v>290</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="C14" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="D14" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="E14" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="F14" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="G14" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="H14" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="B15" s="35">
+        <v>17871826</v>
+      </c>
+      <c r="C15" s="36">
+        <v>247.88</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="E15" s="36">
+        <v>239.12</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="G15" s="36">
+        <v>8.76</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="81" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>302</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B15" s="49">
-        <v>2.4329999999999999E-5</v>
-      </c>
-      <c r="C15" s="36">
-        <v>1.26</v>
-      </c>
-      <c r="D15" s="37" t="s">
+      <c r="E16" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E15" s="36">
-        <v>1.01</v>
-      </c>
-      <c r="F15" s="34" t="s">
+      <c r="F16" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G15" s="36">
-        <v>0.25</v>
-      </c>
-      <c r="H15" s="34" t="s">
+      <c r="G16" s="1" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="74" t="s">
+      <c r="H16" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B16" s="69" t="s">
+    </row>
+    <row r="17" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="B17" s="31">
+        <v>765</v>
+      </c>
+      <c r="C17" s="12">
+        <v>99.19</v>
+      </c>
+      <c r="D17" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E17" s="12">
+        <v>99.9</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="G17" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H17" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="G16" s="1" t="s">
+    </row>
+    <row r="18" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="B18" s="31">
+        <v>3769</v>
+      </c>
+      <c r="C18" s="12">
+        <v>451.76</v>
+      </c>
+      <c r="D18" s="32" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
+      <c r="E18" s="12">
+        <v>456.85</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B17" s="50">
-        <v>0.16664499999999999</v>
-      </c>
-      <c r="C17" s="36">
-        <v>420.12</v>
-      </c>
-      <c r="D17" s="37" t="s">
+      <c r="G18" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="E17" s="36">
-        <v>400.19</v>
-      </c>
-      <c r="F17" s="34" t="s">
+      <c r="H18" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="G17" s="36">
-        <v>19.93</v>
-      </c>
-      <c r="H17" s="34" t="s">
+    </row>
+    <row r="19" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="74" t="s">
+      <c r="B19" s="31">
+        <v>5454</v>
+      </c>
+      <c r="C19" s="12">
+        <v>644.48</v>
+      </c>
+      <c r="D19" s="32" t="s">
         <v>320</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="E19" s="12">
+        <v>648.08000000000004</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="G19" s="32" t="s">
         <v>322</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="H19" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="E18" s="1" t="s">
+    </row>
+    <row r="20" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="B20" s="31">
+        <v>3800</v>
+      </c>
+      <c r="C20" s="12">
+        <v>446.31</v>
+      </c>
+      <c r="D20" s="32" t="s">
         <v>325</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="E20" s="12">
+        <v>448.2</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="G20" s="32" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="H20" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="B19" s="35">
-        <v>17871826</v>
-      </c>
-      <c r="C19" s="36">
-        <v>247.88</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="E19" s="36">
-        <v>239.12</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="G19" s="36">
-        <v>8.76</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="74" t="s">
-        <v>332</v>
-      </c>
-      <c r="B20" s="69" t="s">
-        <v>333</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B21" s="31">
+        <v>1686</v>
+      </c>
+      <c r="C21" s="12">
+        <v>199.66</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="E21" s="12">
+        <v>195.38</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G21" s="12">
+        <v>4.28</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B22" s="31">
+        <v>1672</v>
+      </c>
+      <c r="C22" s="12">
+        <v>198.84</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="E22" s="12">
+        <v>199.86</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23" s="51">
+        <v>244</v>
+      </c>
+      <c r="C23" s="41">
+        <v>29.9</v>
+      </c>
+      <c r="D23" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="E23" s="41">
+        <v>28.7</v>
+      </c>
+      <c r="F23" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="B21" s="31">
-        <v>765</v>
-      </c>
-      <c r="C21" s="12">
-        <v>99.19</v>
-      </c>
-      <c r="D21" s="32" t="s">
+      <c r="G23" s="41">
+        <v>1.2</v>
+      </c>
+      <c r="H23" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="E21" s="12">
-        <v>99.9</v>
-      </c>
-      <c r="F21" s="2" t="s">
+    </row>
+    <row r="24" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="67" t="s">
         <v>342</v>
       </c>
-      <c r="G21" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B22" s="31">
-        <v>3769</v>
-      </c>
-      <c r="C22" s="12">
-        <v>451.76</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>346</v>
-      </c>
-      <c r="E22" s="12">
-        <v>456.85</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B23" s="31">
-        <v>5454</v>
-      </c>
-      <c r="C23" s="12">
-        <v>644.48</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>351</v>
-      </c>
-      <c r="E23" s="12">
-        <v>648.08000000000004</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>353</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B24" s="31">
-        <v>3800</v>
-      </c>
-      <c r="C24" s="12">
-        <v>446.31</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>356</v>
-      </c>
-      <c r="E24" s="12">
-        <v>448.2</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>358</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B25" s="31">
-        <v>1686</v>
-      </c>
-      <c r="C25" s="12">
-        <v>199.66</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>361</v>
-      </c>
-      <c r="E25" s="12">
-        <v>195.38</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="G25" s="12">
-        <v>4.28</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B26" s="31">
-        <v>1672</v>
-      </c>
-      <c r="C26" s="12">
-        <v>198.84</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="E26" s="12">
-        <v>199.86</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="B27" s="51">
-        <v>244</v>
-      </c>
-      <c r="C27" s="41">
-        <v>29.9</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>370</v>
-      </c>
-      <c r="E27" s="41">
-        <v>28.7</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="G27" s="41">
-        <v>1.2</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="63" t="s">
-        <v>373</v>
-      </c>
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="11">
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A28:J28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6114,211 +5305,199 @@
   <sheetData>
     <row r="1" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="J1" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
-        <v>383</v>
-      </c>
-      <c r="B2" s="80" t="s">
-        <v>384</v>
+      <c r="A2" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>353</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>385</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="E2" s="81" t="s">
-        <v>387</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>388</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>389</v>
-      </c>
-      <c r="H2" s="68" t="s">
-        <v>390</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>2024</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>391</v>
-      </c>
+      <c r="B3" s="24"/>
       <c r="C3" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="D3" s="70" t="s">
-        <v>393</v>
-      </c>
-      <c r="E3" s="84" t="s">
-        <v>394</v>
+        <v>355</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>356</v>
+      </c>
+      <c r="E3" s="74" t="s">
+        <v>357</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>396</v>
+        <v>359</v>
       </c>
       <c r="H3" s="43" t="s">
-        <v>397</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
-        <v>398</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="75" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
     </row>
     <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
-        <v>399</v>
-      </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
+      <c r="A5" s="76" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
     </row>
     <row r="6" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
-        <v>400</v>
-      </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
+      <c r="A6" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>404</v>
+        <v>367</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>405</v>
+        <v>368</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>407</v>
+        <v>370</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>409</v>
+        <v>372</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>412</v>
+        <v>375</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>414</v>
+        <v>377</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>416</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>418</v>
+        <v>381</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>420</v>
+        <v>383</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>421</v>
+        <v>384</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>423</v>
+        <v>386</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>424</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="B10" s="31">
         <v>21</v>
@@ -6327,24 +5506,24 @@
         <v>2.4</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>426</v>
+        <v>389</v>
       </c>
       <c r="E10" s="12">
         <v>2.5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>428</v>
+        <v>391</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>429</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>430</v>
+        <v>393</v>
       </c>
       <c r="B11" s="52">
         <v>0.1486152</v>
@@ -6353,24 +5532,24 @@
         <v>0.02</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="E11" s="12">
         <v>0.01</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
       <c r="G11" s="12">
         <v>0.01</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>433</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>434</v>
+        <v>397</v>
       </c>
       <c r="B12" s="31">
         <v>1827</v>
@@ -6379,24 +5558,24 @@
         <v>200.01</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="E12" s="12">
         <v>207.8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>436</v>
+        <v>399</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="B13" s="31">
         <v>1331</v>
@@ -6405,24 +5584,24 @@
         <v>149.78</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="E13" s="12">
         <v>141.58000000000001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="G13" s="12">
         <v>8.1999999999999993</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="B14" s="31">
         <v>3099</v>
@@ -6431,24 +5610,24 @@
         <v>350.04</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="E14" s="12">
         <v>336.43</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>445</v>
+        <v>408</v>
       </c>
       <c r="G14" s="12">
         <v>13.61</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>446</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="B15" s="31">
         <v>1342</v>
@@ -6457,24 +5636,24 @@
         <v>149.91</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>448</v>
+        <v>411</v>
       </c>
       <c r="E15" s="12">
         <v>142.65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>449</v>
+        <v>412</v>
       </c>
       <c r="G15" s="12">
         <v>7.26</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>450</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>451</v>
+        <v>414</v>
       </c>
       <c r="B16" s="31">
         <v>1046</v>
@@ -6483,24 +5662,24 @@
         <v>117.22</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="E16" s="12">
         <v>109.89</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="G16" s="12">
         <v>7.33</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>455</v>
+        <v>418</v>
       </c>
       <c r="B17" s="31">
         <v>3393.12</v>
@@ -6509,24 +5688,24 @@
         <v>359.07</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="E17" s="12">
         <v>366.52</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="G17" s="32" t="s">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="B18" s="31">
         <v>35.18</v>
@@ -6535,24 +5714,24 @@
         <v>3.5</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>461</v>
+        <v>424</v>
       </c>
       <c r="E18" s="12">
         <v>3.77</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>464</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>465</v>
+        <v>428</v>
       </c>
       <c r="B19" s="31">
         <v>517.48</v>
@@ -6561,24 +5740,24 @@
         <v>51.64</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>466</v>
+        <v>429</v>
       </c>
       <c r="E19" s="12">
         <v>50.02</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="G19" s="12">
         <v>1.62</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>468</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="B20" s="31">
         <v>2098.96</v>
@@ -6587,24 +5766,24 @@
         <v>203.19</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="E20" s="12">
         <v>203.93</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G20" s="32" t="s">
-        <v>472</v>
+        <v>435</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>473</v>
+        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>474</v>
+        <v>437</v>
       </c>
       <c r="B21" s="31">
         <v>829.54</v>
@@ -6613,24 +5792,24 @@
         <v>76.48</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="E21" s="12">
         <v>75.010000000000005</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>476</v>
+        <v>439</v>
       </c>
       <c r="G21" s="12">
         <v>1.47</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>477</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="B22" s="31">
         <v>262.49</v>
@@ -6639,24 +5818,24 @@
         <v>23.77</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="E22" s="12">
         <v>24</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="G22" s="32" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="B23" s="31">
         <v>1138.1300000000001</v>
@@ -6665,24 +5844,24 @@
         <v>103.79</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="E23" s="12">
         <v>100</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="G23" s="12">
         <v>3.79</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>487</v>
+        <v>450</v>
       </c>
       <c r="B24" s="31">
         <v>555.85</v>
@@ -6691,24 +5870,24 @@
         <v>51.09</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="E24" s="12">
         <v>50.02</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="G24" s="12">
         <v>1.07</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>490</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>491</v>
+        <v>454</v>
       </c>
       <c r="B25" s="31">
         <v>676.99</v>
@@ -6717,24 +5896,24 @@
         <v>58.74</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="E25" s="12">
         <v>60.02</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="B26" s="31">
         <v>352.64</v>
@@ -6743,24 +5922,24 @@
         <v>35.96</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="E26" s="12">
         <v>35.729999999999997</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="G26" s="12">
         <v>0.23</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="B27" s="31">
         <v>4327.75</v>
@@ -6769,238 +5948,238 @@
         <v>359.69</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="E27" s="12">
         <v>342.13</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="G27" s="12">
         <v>17.559999999999999</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="C28" s="13">
         <v>4366.4399999999996</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>506</v>
+        <v>469</v>
       </c>
       <c r="E28" s="13">
         <v>4328.9799999999996</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="G28" s="13">
         <v>37.46</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>508</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="C29" s="13">
         <v>5035.7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="E29" s="13">
         <v>4969.3</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="G29" s="13">
         <v>66.400000000000006</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>513</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="55" t="s">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>515</v>
+        <v>478</v>
       </c>
       <c r="C30" s="56" t="s">
-        <v>516</v>
+        <v>479</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>517</v>
+        <v>480</v>
       </c>
       <c r="E30" s="56" t="s">
-        <v>518</v>
+        <v>481</v>
       </c>
       <c r="F30" s="56" t="s">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="G30" s="56" t="s">
-        <v>520</v>
+        <v>483</v>
       </c>
       <c r="H30" s="56" t="s">
-        <v>521</v>
+        <v>484</v>
       </c>
       <c r="I30" s="56"/>
       <c r="J30" s="56"/>
     </row>
     <row r="31" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="59" t="s">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="B31" s="60" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="C31" s="60" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="D31" s="60" t="s">
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="E31" s="60" t="s">
-        <v>526</v>
+        <v>489</v>
       </c>
       <c r="F31" s="60" t="s">
-        <v>527</v>
+        <v>490</v>
       </c>
       <c r="G31" s="60" t="s">
-        <v>528</v>
+        <v>491</v>
       </c>
       <c r="H31" s="60" t="s">
-        <v>529</v>
+        <v>492</v>
       </c>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
     </row>
     <row r="32" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="61" t="s">
-        <v>530</v>
+        <v>493</v>
       </c>
       <c r="B32" s="60" t="s">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="D32" s="60" t="s">
-        <v>533</v>
+        <v>496</v>
       </c>
       <c r="E32" s="60" t="s">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="F32" s="60" t="s">
-        <v>535</v>
+        <v>498</v>
       </c>
       <c r="G32" s="60" t="s">
-        <v>536</v>
+        <v>499</v>
       </c>
       <c r="H32" s="60" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="I32" s="56"/>
       <c r="J32" s="56"/>
     </row>
     <row r="33" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>539</v>
+        <v>502</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>542</v>
+        <v>505</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>543</v>
+        <v>506</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>545</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>547</v>
+        <v>510</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="D34" s="48" t="s">
-        <v>549</v>
+        <v>512</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>552</v>
+        <v>515</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>553</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
-        <v>554</v>
+        <v>517</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>558</v>
+        <v>521</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>559</v>
+        <v>522</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="B36" s="53">
         <v>9.1999999999999998E-7</v>
@@ -7009,60 +6188,60 @@
         <v>0</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
       <c r="E36" s="12">
         <v>0</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>564</v>
+        <v>527</v>
       </c>
       <c r="G36" s="5">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45" t="s">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>567</v>
+        <v>530</v>
       </c>
       <c r="C37" s="54">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="E37" s="46">
         <v>0</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>569</v>
+        <v>532</v>
       </c>
       <c r="G37" s="54">
         <v>0</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>570</v>
+        <v>533</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="63" t="s">
-        <v>571</v>
-      </c>
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
+      <c r="A38" s="67" t="s">
+        <v>534</v>
+      </c>
+      <c r="B38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7096,225 +6275,213 @@
   <sheetData>
     <row r="1" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>572</v>
+        <v>535</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>573</v>
+        <v>536</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>574</v>
+        <v>537</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>575</v>
+        <v>538</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>576</v>
+        <v>539</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>577</v>
+        <v>540</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>578</v>
+        <v>541</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>579</v>
+        <v>542</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="J1" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
-        <v>581</v>
-      </c>
-      <c r="B2" s="80" t="s">
-        <v>582</v>
+      <c r="A2" s="68" t="s">
+        <v>544</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>545</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>583</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>584</v>
-      </c>
-      <c r="E2" s="81" t="s">
-        <v>585</v>
-      </c>
-      <c r="F2" s="67" t="s">
-        <v>586</v>
-      </c>
-      <c r="G2" s="67" t="s">
-        <v>587</v>
-      </c>
-      <c r="H2" s="68" t="s">
-        <v>588</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
         <v>2024</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>589</v>
-      </c>
+      <c r="B3" s="24"/>
       <c r="C3" s="19" t="s">
-        <v>590</v>
-      </c>
-      <c r="D3" s="70" t="s">
-        <v>591</v>
-      </c>
-      <c r="E3" s="84" t="s">
-        <v>592</v>
+        <v>547</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>548</v>
+      </c>
+      <c r="E3" s="74" t="s">
+        <v>549</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>593</v>
+        <v>550</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>594</v>
+        <v>551</v>
       </c>
       <c r="H3" s="43" t="s">
-        <v>595</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
-        <v>596</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="75" t="s">
+        <v>553</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
     </row>
     <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
-        <v>597</v>
-      </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
+      <c r="A5" s="76" t="s">
+        <v>554</v>
+      </c>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
     </row>
     <row r="6" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
-        <v>598</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>599</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>600</v>
-      </c>
-      <c r="D6" s="69" t="s">
-        <v>601</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>602</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>603</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>604</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>605</v>
-      </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
+      <c r="A6" s="62" t="s">
+        <v>555</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>556</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>557</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>558</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>559</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>560</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>561</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>562</v>
+      </c>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>606</v>
+        <v>563</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>607</v>
+        <v>564</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>608</v>
+        <v>565</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>609</v>
+        <v>566</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>610</v>
+        <v>567</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>611</v>
+        <v>568</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>612</v>
+        <v>569</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>613</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>614</v>
+        <v>571</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>615</v>
+        <v>572</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>617</v>
+        <v>574</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>618</v>
+        <v>575</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>619</v>
+        <v>576</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>620</v>
+        <v>577</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>621</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="66" t="s">
-        <v>622</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>623</v>
+      <c r="A9" s="65" t="s">
+        <v>579</v>
+      </c>
+      <c r="B9" s="66" t="s">
+        <v>580</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>624</v>
+        <v>581</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>625</v>
+        <v>582</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>626</v>
+        <v>583</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>627</v>
+        <v>584</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>628</v>
+        <v>585</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>629</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>630</v>
+        <v>587</v>
       </c>
       <c r="B10" s="31">
         <v>95</v>
@@ -7323,24 +6490,24 @@
         <v>10.95</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>631</v>
+        <v>588</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>632</v>
+        <v>589</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>633</v>
+        <v>590</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>634</v>
+        <v>591</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>635</v>
+        <v>592</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>636</v>
+        <v>593</v>
       </c>
       <c r="B11" s="52">
         <v>39.851384799999998</v>
@@ -7349,24 +6516,24 @@
         <v>5.2</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>637</v>
+        <v>594</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>638</v>
+        <v>595</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>639</v>
+        <v>596</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>640</v>
+        <v>597</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>641</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>642</v>
+        <v>599</v>
       </c>
       <c r="B12" s="31">
         <v>3000</v>
@@ -7375,24 +6542,24 @@
         <v>298.47000000000003</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>643</v>
+        <v>600</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>644</v>
+        <v>601</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>645</v>
+        <v>602</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>646</v>
+        <v>603</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>647</v>
+        <v>604</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>648</v>
+        <v>605</v>
       </c>
       <c r="B13" s="31">
         <v>900</v>
@@ -7401,24 +6568,24 @@
         <v>81.5</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>649</v>
+        <v>606</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>650</v>
+        <v>607</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>651</v>
+        <v>608</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>652</v>
+        <v>609</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>653</v>
+        <v>610</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>654</v>
+        <v>611</v>
       </c>
       <c r="B14" s="31">
         <v>1900</v>
@@ -7427,24 +6594,24 @@
         <v>192.83</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>655</v>
+        <v>612</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>656</v>
+        <v>613</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>657</v>
+        <v>614</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>658</v>
+        <v>615</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>659</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>660</v>
+        <v>617</v>
       </c>
       <c r="B15" s="31">
         <v>2837.36</v>
@@ -7453,24 +6620,24 @@
         <v>269.95</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>661</v>
+        <v>618</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>662</v>
+        <v>619</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>663</v>
+        <v>620</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>664</v>
+        <v>621</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>665</v>
+        <v>622</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>666</v>
+        <v>623</v>
       </c>
       <c r="B16" s="31">
         <v>58.31</v>
@@ -7479,24 +6646,24 @@
         <v>6</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>667</v>
+        <v>624</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>668</v>
+        <v>625</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>669</v>
+        <v>626</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>670</v>
+        <v>627</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>671</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>672</v>
+        <v>629</v>
       </c>
       <c r="B17" s="31">
         <v>11306.33</v>
@@ -7505,24 +6672,24 @@
         <v>1104.79</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>673</v>
+        <v>630</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>674</v>
+        <v>631</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>675</v>
+        <v>632</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>676</v>
+        <v>633</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>677</v>
+        <v>634</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>678</v>
+        <v>635</v>
       </c>
       <c r="B18" s="31">
         <v>6800</v>
@@ -7531,24 +6698,24 @@
         <v>668.8</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>679</v>
+        <v>636</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>680</v>
+        <v>637</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>681</v>
+        <v>638</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>682</v>
+        <v>639</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>683</v>
+        <v>640</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>684</v>
+        <v>641</v>
       </c>
       <c r="B19" s="31">
         <v>180</v>
@@ -7557,24 +6724,24 @@
         <v>16.98</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>685</v>
+        <v>642</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>686</v>
+        <v>643</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>687</v>
+        <v>644</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>688</v>
+        <v>645</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>689</v>
+        <v>646</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>690</v>
+        <v>647</v>
       </c>
       <c r="B20" s="31">
         <v>418</v>
@@ -7583,24 +6750,24 @@
         <v>38.340000000000003</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>691</v>
+        <v>648</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>692</v>
+        <v>649</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>693</v>
+        <v>650</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>694</v>
+        <v>651</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>695</v>
+        <v>652</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>696</v>
+        <v>653</v>
       </c>
       <c r="B21" s="31">
         <v>88.78</v>
@@ -7609,24 +6776,24 @@
         <v>9.48</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>697</v>
+        <v>654</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>698</v>
+        <v>655</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>699</v>
+        <v>656</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>700</v>
+        <v>657</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>701</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>702</v>
+        <v>659</v>
       </c>
       <c r="B22" s="31">
         <v>45</v>
@@ -7635,24 +6802,24 @@
         <v>8.83</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>703</v>
+        <v>660</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>704</v>
+        <v>661</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>705</v>
+        <v>662</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>706</v>
+        <v>663</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>707</v>
+        <v>664</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>708</v>
+        <v>665</v>
       </c>
       <c r="B23" s="31">
         <v>44</v>
@@ -7661,24 +6828,24 @@
         <v>10.89</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>710</v>
+        <v>667</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>711</v>
+        <v>668</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>712</v>
+        <v>669</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>713</v>
+        <v>670</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>714</v>
+        <v>671</v>
       </c>
       <c r="B24" s="31">
         <v>38</v>
@@ -7687,86 +6854,86 @@
         <v>18.149999999999999</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>715</v>
+        <v>672</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>716</v>
+        <v>673</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>717</v>
+        <v>674</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>718</v>
+        <v>675</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>719</v>
+        <v>676</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>720</v>
+        <v>677</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>721</v>
+        <v>678</v>
       </c>
       <c r="C25" s="13">
         <v>2741.16</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>722</v>
+        <v>679</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>723</v>
+        <v>680</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>724</v>
+        <v>681</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>725</v>
+        <v>682</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45" t="s">
-        <v>727</v>
+        <v>684</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>728</v>
+        <v>685</v>
       </c>
       <c r="C26" s="46">
         <v>2741.16</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>730</v>
+        <v>687</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>731</v>
+        <v>688</v>
       </c>
       <c r="G26" s="45" t="s">
-        <v>732</v>
+        <v>689</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>733</v>
+        <v>690</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="63" t="s">
-        <v>734</v>
-      </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
+      <c r="A27" s="67" t="s">
+        <v>691</v>
+      </c>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="8">
